--- a/RVI20U32/Docs/IF_Verifications/IF_verification_template.xlsx
+++ b/RVI20U32/Docs/IF_Verifications/IF_verification_template.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,12 +8,12 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Test_Definition" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Signals_Observed" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="IF_001_seq" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="IF_002_seq" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="IF_003_flush" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="IF_004_hold" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="Test_Definition" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Signals_Observed" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="IF_001_seq" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="IF_002_seq" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="IF_003_flush" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="IF_004_hold" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
   <si>
     <t xml:space="preserve">Test ID</t>
   </si>
@@ -237,6 +237,9 @@
     <t xml:space="preserve">6f </t>
   </si>
   <si>
+    <t xml:space="preserve">PASSED</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST 1</t>
   </si>
   <si>
@@ -262,6 +265,9 @@
   </si>
   <si>
     <t xml:space="preserve">target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO FLUSHING </t>
   </si>
 </sst>
 </file>
@@ -271,7 +277,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -295,10 +301,19 @@
       <family val="0"/>
     </font>
     <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF72BF44"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -413,72 +428,140 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF72BF44"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -486,20 +569,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>795960</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>118440</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>55440</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>474480</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>56160</xdr:rowOff>
+      <xdr:colOff>465120</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>38160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Imagen 1" descr=""/>
+        <xdr:cNvPr id="1" name="Imagen 1"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -508,13 +591,14 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="795960" y="3974040"/>
-          <a:ext cx="12907800" cy="5020200"/>
+          <a:off x="786960" y="2028600"/>
+          <a:ext cx="11580480" cy="5019840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -530,18 +614,18 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>111960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>207720</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>123840</xdr:rowOff>
+      <xdr:colOff>207360</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Imagen 2" descr=""/>
+        <xdr:cNvPr id="2" name="Imagen 2"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -550,13 +634,14 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="812520" y="812520"/>
-          <a:ext cx="15651000" cy="2399760"/>
+          <a:off x="731520" y="812880"/>
+          <a:ext cx="14106240" cy="2399400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -567,18 +652,18 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>723600</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>64080</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>84240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>366480</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>78120</xdr:rowOff>
+      <xdr:colOff>366120</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>95760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 3" descr=""/>
+        <xdr:cNvPr id="3" name="Imagen 3"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -588,12 +673,13 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="723600" y="4465800"/>
-          <a:ext cx="15898680" cy="2640240"/>
+          <a:ext cx="14272920" cy="2640240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -603,129 +689,278 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>-360</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>132120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>84600</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>131760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1364760" y="1884600"/>
+          <a:ext cx="18251640" cy="2628720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B3:F8"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="31.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="7" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="7" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>28</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -734,103 +969,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="C3:D12"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -839,104 +1074,104 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:G10"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:G43"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="5.21"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="5.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>100093</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="12" t="n">
@@ -947,16 +1182,16 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>61</v>
       </c>
       <c r="F7" s="12" t="n">
@@ -967,16 +1202,16 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>63</v>
       </c>
       <c r="F8" s="12" t="n">
@@ -987,16 +1222,16 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="12" t="n">
@@ -1007,16 +1242,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>67</v>
       </c>
       <c r="F10" s="12" t="s">
@@ -1026,10 +1261,18 @@
         <v>58</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -1039,278 +1282,335 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B48"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B1:B51"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="14" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="0" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Página &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Página &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C3:J7"/>
-  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="C3:J10"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="8.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="8" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="E5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="E6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/RVI20U32/Docs/IF_Verifications/IF_verification_template.xlsx
+++ b/RVI20U32/Docs/IF_Verifications/IF_verification_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Definition" sheetId="1" state="visible" r:id="rId3"/>
@@ -14,6 +14,7 @@
     <sheet name="IF_002_seq" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="IF_003_flush" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="IF_004_hold" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="IF_005_reset_vio" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="85">
   <si>
     <t xml:space="preserve">Test ID</t>
   </si>
@@ -268,6 +269,18 @@
   </si>
   <si>
     <t xml:space="preserve">NO FLUSHING </t>
+  </si>
+  <si>
+    <t xml:space="preserve">When PC_REDIRECT_VALID =1 next instruction out from IF is a NOP and Valid_out =0 is a no valid instruction here is killed the 2 instruction bellow branch beq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIO deactivate the reset and instruction start to get out from BRAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIO like RESET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIO like HOLD</t>
   </si>
 </sst>
 </file>
@@ -576,9 +589,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>465120</xdr:colOff>
+      <xdr:colOff>464760</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>38160</xdr:rowOff>
+      <xdr:rowOff>37800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -592,7 +605,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="786960" y="2028600"/>
-          <a:ext cx="11580480" cy="5019840"/>
+          <a:ext cx="11580120" cy="5019480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -619,9 +632,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>207360</xdr:colOff>
+      <xdr:colOff>207000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>57600</xdr:rowOff>
+      <xdr:rowOff>57240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -635,7 +648,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="731520" y="812880"/>
-          <a:ext cx="14106240" cy="2399400"/>
+          <a:ext cx="14105880" cy="2399040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -657,9 +670,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>366120</xdr:colOff>
+      <xdr:colOff>365760</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>95760</xdr:rowOff>
+      <xdr:rowOff>95400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -673,7 +686,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="723600" y="4465800"/>
-          <a:ext cx="14272920" cy="2640240"/>
+          <a:ext cx="14272560" cy="2639880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -700,9 +713,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>84600</xdr:colOff>
+      <xdr:colOff>84240</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>131760</xdr:rowOff>
+      <xdr:rowOff>131400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -716,7 +729,164 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1364760" y="1884600"/>
-          <a:ext cx="18251640" cy="2628720"/>
+          <a:ext cx="18251280" cy="2628360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>360</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>11520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>75240</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>137880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1365480" y="5795280"/>
+          <a:ext cx="18241560" cy="2930400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>793080</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>38160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>633960</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>104760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image 3"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="793080" y="1176120"/>
+          <a:ext cx="16909560" cy="2829960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9720</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>117000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>673200</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>20880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 4"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="822600" y="9220320"/>
+          <a:ext cx="16106760" cy="2829960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>790920</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>66600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>324360</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>37440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 5"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="790920" y="5268600"/>
+          <a:ext cx="18227880" cy="3222000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1380,7 +1550,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="C3:J10"/>
+  <dimension ref="C3:J53"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="8.53"/>
@@ -1503,6 +1673,16 @@
       </c>
       <c r="D10" s="1" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C53" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1522,90 +1702,1137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="B1:AML6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1026" min="9" style="1" width="8.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="B1" s="0"/>
+      <c r="C1" s="0"/>
+      <c r="D1" s="0"/>
+      <c r="E1" s="0"/>
+      <c r="F1" s="0"/>
+      <c r="G1" s="0"/>
+      <c r="H1" s="0"/>
+      <c r="I1" s="0"/>
+      <c r="J1" s="0"/>
+      <c r="K1" s="0"/>
+      <c r="L1" s="0"/>
+      <c r="M1" s="0"/>
+      <c r="N1" s="0"/>
+      <c r="O1" s="0"/>
+      <c r="P1" s="0"/>
+      <c r="Q1" s="0"/>
+      <c r="R1" s="0"/>
+      <c r="S1" s="0"/>
+      <c r="T1" s="0"/>
+      <c r="U1" s="0"/>
+      <c r="V1" s="0"/>
+      <c r="W1" s="0"/>
+      <c r="X1" s="0"/>
+      <c r="Y1" s="0"/>
+      <c r="Z1" s="0"/>
+      <c r="AA1" s="0"/>
+      <c r="AB1" s="0"/>
+      <c r="AC1" s="0"/>
+      <c r="AD1" s="0"/>
+      <c r="AE1" s="0"/>
+      <c r="AF1" s="0"/>
+      <c r="AG1" s="0"/>
+      <c r="AH1" s="0"/>
+      <c r="AI1" s="0"/>
+      <c r="AJ1" s="0"/>
+      <c r="AK1" s="0"/>
+      <c r="AL1" s="0"/>
+      <c r="AM1" s="0"/>
+      <c r="AN1" s="0"/>
+      <c r="AO1" s="0"/>
+      <c r="AP1" s="0"/>
+      <c r="AQ1" s="0"/>
+      <c r="AR1" s="0"/>
+      <c r="AS1" s="0"/>
+      <c r="AT1" s="0"/>
+      <c r="AU1" s="0"/>
+      <c r="AV1" s="0"/>
+      <c r="AW1" s="0"/>
+      <c r="AX1" s="0"/>
+      <c r="AY1" s="0"/>
+      <c r="AZ1" s="0"/>
+      <c r="BA1" s="0"/>
+      <c r="BB1" s="0"/>
+      <c r="BC1" s="0"/>
+      <c r="BD1" s="0"/>
+      <c r="BE1" s="0"/>
+      <c r="BF1" s="0"/>
+      <c r="BG1" s="0"/>
+      <c r="BH1" s="0"/>
+      <c r="BI1" s="0"/>
+      <c r="BJ1" s="0"/>
+      <c r="BK1" s="0"/>
+      <c r="BL1" s="0"/>
+      <c r="BM1" s="0"/>
+      <c r="BN1" s="0"/>
+      <c r="BO1" s="0"/>
+      <c r="BP1" s="0"/>
+      <c r="BQ1" s="0"/>
+      <c r="BR1" s="0"/>
+      <c r="BS1" s="0"/>
+      <c r="BT1" s="0"/>
+      <c r="BU1" s="0"/>
+      <c r="BV1" s="0"/>
+      <c r="BW1" s="0"/>
+      <c r="BX1" s="0"/>
+      <c r="BY1" s="0"/>
+      <c r="BZ1" s="0"/>
+      <c r="CA1" s="0"/>
+      <c r="CB1" s="0"/>
+      <c r="CC1" s="0"/>
+      <c r="CD1" s="0"/>
+      <c r="CE1" s="0"/>
+      <c r="CF1" s="0"/>
+      <c r="CG1" s="0"/>
+      <c r="CH1" s="0"/>
+      <c r="CI1" s="0"/>
+      <c r="CJ1" s="0"/>
+      <c r="CK1" s="0"/>
+      <c r="CL1" s="0"/>
+      <c r="CM1" s="0"/>
+      <c r="CN1" s="0"/>
+      <c r="CO1" s="0"/>
+      <c r="CP1" s="0"/>
+      <c r="CQ1" s="0"/>
+      <c r="CR1" s="0"/>
+      <c r="CS1" s="0"/>
+      <c r="CT1" s="0"/>
+      <c r="CU1" s="0"/>
+      <c r="CV1" s="0"/>
+      <c r="CW1" s="0"/>
+      <c r="CX1" s="0"/>
+      <c r="CY1" s="0"/>
+      <c r="CZ1" s="0"/>
+      <c r="DA1" s="0"/>
+      <c r="DB1" s="0"/>
+      <c r="DC1" s="0"/>
+      <c r="DD1" s="0"/>
+      <c r="DE1" s="0"/>
+      <c r="DF1" s="0"/>
+      <c r="DG1" s="0"/>
+      <c r="DH1" s="0"/>
+      <c r="DI1" s="0"/>
+      <c r="DJ1" s="0"/>
+      <c r="DK1" s="0"/>
+      <c r="DL1" s="0"/>
+      <c r="DM1" s="0"/>
+      <c r="DN1" s="0"/>
+      <c r="DO1" s="0"/>
+      <c r="DP1" s="0"/>
+      <c r="DQ1" s="0"/>
+      <c r="DR1" s="0"/>
+      <c r="DS1" s="0"/>
+      <c r="DT1" s="0"/>
+      <c r="DU1" s="0"/>
+      <c r="DV1" s="0"/>
+      <c r="DW1" s="0"/>
+      <c r="DX1" s="0"/>
+      <c r="DY1" s="0"/>
+      <c r="DZ1" s="0"/>
+      <c r="EA1" s="0"/>
+      <c r="EB1" s="0"/>
+      <c r="EC1" s="0"/>
+      <c r="ED1" s="0"/>
+      <c r="EE1" s="0"/>
+      <c r="EF1" s="0"/>
+      <c r="EG1" s="0"/>
+      <c r="EH1" s="0"/>
+      <c r="EI1" s="0"/>
+      <c r="EJ1" s="0"/>
+      <c r="EK1" s="0"/>
+      <c r="EL1" s="0"/>
+      <c r="EM1" s="0"/>
+      <c r="EN1" s="0"/>
+      <c r="EO1" s="0"/>
+      <c r="EP1" s="0"/>
+      <c r="EQ1" s="0"/>
+      <c r="ER1" s="0"/>
+      <c r="ES1" s="0"/>
+      <c r="ET1" s="0"/>
+      <c r="EU1" s="0"/>
+      <c r="EV1" s="0"/>
+      <c r="EW1" s="0"/>
+      <c r="EX1" s="0"/>
+      <c r="EY1" s="0"/>
+      <c r="EZ1" s="0"/>
+      <c r="FA1" s="0"/>
+      <c r="FB1" s="0"/>
+      <c r="FC1" s="0"/>
+      <c r="FD1" s="0"/>
+      <c r="FE1" s="0"/>
+      <c r="FF1" s="0"/>
+      <c r="FG1" s="0"/>
+      <c r="FH1" s="0"/>
+      <c r="FI1" s="0"/>
+      <c r="FJ1" s="0"/>
+      <c r="FK1" s="0"/>
+      <c r="FL1" s="0"/>
+      <c r="FM1" s="0"/>
+      <c r="FN1" s="0"/>
+      <c r="FO1" s="0"/>
+      <c r="FP1" s="0"/>
+      <c r="FQ1" s="0"/>
+      <c r="FR1" s="0"/>
+      <c r="FS1" s="0"/>
+      <c r="FT1" s="0"/>
+      <c r="FU1" s="0"/>
+      <c r="FV1" s="0"/>
+      <c r="FW1" s="0"/>
+      <c r="FX1" s="0"/>
+      <c r="FY1" s="0"/>
+      <c r="FZ1" s="0"/>
+      <c r="GA1" s="0"/>
+      <c r="GB1" s="0"/>
+      <c r="GC1" s="0"/>
+      <c r="GD1" s="0"/>
+      <c r="GE1" s="0"/>
+      <c r="GF1" s="0"/>
+      <c r="GG1" s="0"/>
+      <c r="GH1" s="0"/>
+      <c r="GI1" s="0"/>
+      <c r="GJ1" s="0"/>
+      <c r="GK1" s="0"/>
+      <c r="GL1" s="0"/>
+      <c r="GM1" s="0"/>
+      <c r="GN1" s="0"/>
+      <c r="GO1" s="0"/>
+      <c r="GP1" s="0"/>
+      <c r="GQ1" s="0"/>
+      <c r="GR1" s="0"/>
+      <c r="GS1" s="0"/>
+      <c r="GT1" s="0"/>
+      <c r="GU1" s="0"/>
+      <c r="GV1" s="0"/>
+      <c r="GW1" s="0"/>
+      <c r="GX1" s="0"/>
+      <c r="GY1" s="0"/>
+      <c r="GZ1" s="0"/>
+      <c r="HA1" s="0"/>
+      <c r="HB1" s="0"/>
+      <c r="HC1" s="0"/>
+      <c r="HD1" s="0"/>
+      <c r="HE1" s="0"/>
+      <c r="HF1" s="0"/>
+      <c r="HG1" s="0"/>
+      <c r="HH1" s="0"/>
+      <c r="HI1" s="0"/>
+      <c r="HJ1" s="0"/>
+      <c r="HK1" s="0"/>
+      <c r="HL1" s="0"/>
+      <c r="HM1" s="0"/>
+      <c r="HN1" s="0"/>
+      <c r="HO1" s="0"/>
+      <c r="HP1" s="0"/>
+      <c r="HQ1" s="0"/>
+      <c r="HR1" s="0"/>
+      <c r="HS1" s="0"/>
+      <c r="HT1" s="0"/>
+      <c r="HU1" s="0"/>
+      <c r="HV1" s="0"/>
+      <c r="HW1" s="0"/>
+      <c r="HX1" s="0"/>
+      <c r="HY1" s="0"/>
+      <c r="HZ1" s="0"/>
+      <c r="IA1" s="0"/>
+      <c r="IB1" s="0"/>
+      <c r="IC1" s="0"/>
+      <c r="ID1" s="0"/>
+      <c r="IE1" s="0"/>
+      <c r="IF1" s="0"/>
+      <c r="IG1" s="0"/>
+      <c r="IH1" s="0"/>
+      <c r="II1" s="0"/>
+      <c r="IJ1" s="0"/>
+      <c r="IK1" s="0"/>
+      <c r="IL1" s="0"/>
+      <c r="IM1" s="0"/>
+      <c r="IN1" s="0"/>
+      <c r="IO1" s="0"/>
+      <c r="IP1" s="0"/>
+      <c r="IQ1" s="0"/>
+      <c r="IR1" s="0"/>
+      <c r="IS1" s="0"/>
+      <c r="IT1" s="0"/>
+      <c r="IU1" s="0"/>
+      <c r="IV1" s="0"/>
+      <c r="IW1" s="0"/>
+      <c r="IX1" s="0"/>
+      <c r="IY1" s="0"/>
+      <c r="IZ1" s="0"/>
+      <c r="JA1" s="0"/>
+      <c r="JB1" s="0"/>
+      <c r="JC1" s="0"/>
+      <c r="JD1" s="0"/>
+      <c r="JE1" s="0"/>
+      <c r="JF1" s="0"/>
+      <c r="JG1" s="0"/>
+      <c r="JH1" s="0"/>
+      <c r="JI1" s="0"/>
+      <c r="JJ1" s="0"/>
+      <c r="JK1" s="0"/>
+      <c r="JL1" s="0"/>
+      <c r="JM1" s="0"/>
+      <c r="JN1" s="0"/>
+      <c r="JO1" s="0"/>
+      <c r="JP1" s="0"/>
+      <c r="JQ1" s="0"/>
+      <c r="JR1" s="0"/>
+      <c r="JS1" s="0"/>
+      <c r="JT1" s="0"/>
+      <c r="JU1" s="0"/>
+      <c r="JV1" s="0"/>
+      <c r="JW1" s="0"/>
+      <c r="JX1" s="0"/>
+      <c r="JY1" s="0"/>
+      <c r="JZ1" s="0"/>
+      <c r="KA1" s="0"/>
+      <c r="KB1" s="0"/>
+      <c r="KC1" s="0"/>
+      <c r="KD1" s="0"/>
+      <c r="KE1" s="0"/>
+      <c r="KF1" s="0"/>
+      <c r="KG1" s="0"/>
+      <c r="KH1" s="0"/>
+      <c r="KI1" s="0"/>
+      <c r="KJ1" s="0"/>
+      <c r="KK1" s="0"/>
+      <c r="KL1" s="0"/>
+      <c r="KM1" s="0"/>
+      <c r="KN1" s="0"/>
+      <c r="KO1" s="0"/>
+      <c r="KP1" s="0"/>
+      <c r="KQ1" s="0"/>
+      <c r="KR1" s="0"/>
+      <c r="KS1" s="0"/>
+      <c r="KT1" s="0"/>
+      <c r="KU1" s="0"/>
+      <c r="KV1" s="0"/>
+      <c r="KW1" s="0"/>
+      <c r="KX1" s="0"/>
+      <c r="KY1" s="0"/>
+      <c r="KZ1" s="0"/>
+      <c r="LA1" s="0"/>
+      <c r="LB1" s="0"/>
+      <c r="LC1" s="0"/>
+      <c r="LD1" s="0"/>
+      <c r="LE1" s="0"/>
+      <c r="LF1" s="0"/>
+      <c r="LG1" s="0"/>
+      <c r="LH1" s="0"/>
+      <c r="LI1" s="0"/>
+      <c r="LJ1" s="0"/>
+      <c r="LK1" s="0"/>
+      <c r="LL1" s="0"/>
+      <c r="LM1" s="0"/>
+      <c r="LN1" s="0"/>
+      <c r="LO1" s="0"/>
+      <c r="LP1" s="0"/>
+      <c r="LQ1" s="0"/>
+      <c r="LR1" s="0"/>
+      <c r="LS1" s="0"/>
+      <c r="LT1" s="0"/>
+      <c r="LU1" s="0"/>
+      <c r="LV1" s="0"/>
+      <c r="LW1" s="0"/>
+      <c r="LX1" s="0"/>
+      <c r="LY1" s="0"/>
+      <c r="LZ1" s="0"/>
+      <c r="MA1" s="0"/>
+      <c r="MB1" s="0"/>
+      <c r="MC1" s="0"/>
+      <c r="MD1" s="0"/>
+      <c r="ME1" s="0"/>
+      <c r="MF1" s="0"/>
+      <c r="MG1" s="0"/>
+      <c r="MH1" s="0"/>
+      <c r="MI1" s="0"/>
+      <c r="MJ1" s="0"/>
+      <c r="MK1" s="0"/>
+      <c r="ML1" s="0"/>
+      <c r="MM1" s="0"/>
+      <c r="MN1" s="0"/>
+      <c r="MO1" s="0"/>
+      <c r="MP1" s="0"/>
+      <c r="MQ1" s="0"/>
+      <c r="MR1" s="0"/>
+      <c r="MS1" s="0"/>
+      <c r="MT1" s="0"/>
+      <c r="MU1" s="0"/>
+      <c r="MV1" s="0"/>
+      <c r="MW1" s="0"/>
+      <c r="MX1" s="0"/>
+      <c r="MY1" s="0"/>
+      <c r="MZ1" s="0"/>
+      <c r="NA1" s="0"/>
+      <c r="NB1" s="0"/>
+      <c r="NC1" s="0"/>
+      <c r="ND1" s="0"/>
+      <c r="NE1" s="0"/>
+      <c r="NF1" s="0"/>
+      <c r="NG1" s="0"/>
+      <c r="NH1" s="0"/>
+      <c r="NI1" s="0"/>
+      <c r="NJ1" s="0"/>
+      <c r="NK1" s="0"/>
+      <c r="NL1" s="0"/>
+      <c r="NM1" s="0"/>
+      <c r="NN1" s="0"/>
+      <c r="NO1" s="0"/>
+      <c r="NP1" s="0"/>
+      <c r="NQ1" s="0"/>
+      <c r="NR1" s="0"/>
+      <c r="NS1" s="0"/>
+      <c r="NT1" s="0"/>
+      <c r="NU1" s="0"/>
+      <c r="NV1" s="0"/>
+      <c r="NW1" s="0"/>
+      <c r="NX1" s="0"/>
+      <c r="NY1" s="0"/>
+      <c r="NZ1" s="0"/>
+      <c r="OA1" s="0"/>
+      <c r="OB1" s="0"/>
+      <c r="OC1" s="0"/>
+      <c r="OD1" s="0"/>
+      <c r="OE1" s="0"/>
+      <c r="OF1" s="0"/>
+      <c r="OG1" s="0"/>
+      <c r="OH1" s="0"/>
+      <c r="OI1" s="0"/>
+      <c r="OJ1" s="0"/>
+      <c r="OK1" s="0"/>
+      <c r="OL1" s="0"/>
+      <c r="OM1" s="0"/>
+      <c r="ON1" s="0"/>
+      <c r="OO1" s="0"/>
+      <c r="OP1" s="0"/>
+      <c r="OQ1" s="0"/>
+      <c r="OR1" s="0"/>
+      <c r="OS1" s="0"/>
+      <c r="OT1" s="0"/>
+      <c r="OU1" s="0"/>
+      <c r="OV1" s="0"/>
+      <c r="OW1" s="0"/>
+      <c r="OX1" s="0"/>
+      <c r="OY1" s="0"/>
+      <c r="OZ1" s="0"/>
+      <c r="PA1" s="0"/>
+      <c r="PB1" s="0"/>
+      <c r="PC1" s="0"/>
+      <c r="PD1" s="0"/>
+      <c r="PE1" s="0"/>
+      <c r="PF1" s="0"/>
+      <c r="PG1" s="0"/>
+      <c r="PH1" s="0"/>
+      <c r="PI1" s="0"/>
+      <c r="PJ1" s="0"/>
+      <c r="PK1" s="0"/>
+      <c r="PL1" s="0"/>
+      <c r="PM1" s="0"/>
+      <c r="PN1" s="0"/>
+      <c r="PO1" s="0"/>
+      <c r="PP1" s="0"/>
+      <c r="PQ1" s="0"/>
+      <c r="PR1" s="0"/>
+      <c r="PS1" s="0"/>
+      <c r="PT1" s="0"/>
+      <c r="PU1" s="0"/>
+      <c r="PV1" s="0"/>
+      <c r="PW1" s="0"/>
+      <c r="PX1" s="0"/>
+      <c r="PY1" s="0"/>
+      <c r="PZ1" s="0"/>
+      <c r="QA1" s="0"/>
+      <c r="QB1" s="0"/>
+      <c r="QC1" s="0"/>
+      <c r="QD1" s="0"/>
+      <c r="QE1" s="0"/>
+      <c r="QF1" s="0"/>
+      <c r="QG1" s="0"/>
+      <c r="QH1" s="0"/>
+      <c r="QI1" s="0"/>
+      <c r="QJ1" s="0"/>
+      <c r="QK1" s="0"/>
+      <c r="QL1" s="0"/>
+      <c r="QM1" s="0"/>
+      <c r="QN1" s="0"/>
+      <c r="QO1" s="0"/>
+      <c r="QP1" s="0"/>
+      <c r="QQ1" s="0"/>
+      <c r="QR1" s="0"/>
+      <c r="QS1" s="0"/>
+      <c r="QT1" s="0"/>
+      <c r="QU1" s="0"/>
+      <c r="QV1" s="0"/>
+      <c r="QW1" s="0"/>
+      <c r="QX1" s="0"/>
+      <c r="QY1" s="0"/>
+      <c r="QZ1" s="0"/>
+      <c r="RA1" s="0"/>
+      <c r="RB1" s="0"/>
+      <c r="RC1" s="0"/>
+      <c r="RD1" s="0"/>
+      <c r="RE1" s="0"/>
+      <c r="RF1" s="0"/>
+      <c r="RG1" s="0"/>
+      <c r="RH1" s="0"/>
+      <c r="RI1" s="0"/>
+      <c r="RJ1" s="0"/>
+      <c r="RK1" s="0"/>
+      <c r="RL1" s="0"/>
+      <c r="RM1" s="0"/>
+      <c r="RN1" s="0"/>
+      <c r="RO1" s="0"/>
+      <c r="RP1" s="0"/>
+      <c r="RQ1" s="0"/>
+      <c r="RR1" s="0"/>
+      <c r="RS1" s="0"/>
+      <c r="RT1" s="0"/>
+      <c r="RU1" s="0"/>
+      <c r="RV1" s="0"/>
+      <c r="RW1" s="0"/>
+      <c r="RX1" s="0"/>
+      <c r="RY1" s="0"/>
+      <c r="RZ1" s="0"/>
+      <c r="SA1" s="0"/>
+      <c r="SB1" s="0"/>
+      <c r="SC1" s="0"/>
+      <c r="SD1" s="0"/>
+      <c r="SE1" s="0"/>
+      <c r="SF1" s="0"/>
+      <c r="SG1" s="0"/>
+      <c r="SH1" s="0"/>
+      <c r="SI1" s="0"/>
+      <c r="SJ1" s="0"/>
+      <c r="SK1" s="0"/>
+      <c r="SL1" s="0"/>
+      <c r="SM1" s="0"/>
+      <c r="SN1" s="0"/>
+      <c r="SO1" s="0"/>
+      <c r="SP1" s="0"/>
+      <c r="SQ1" s="0"/>
+      <c r="SR1" s="0"/>
+      <c r="SS1" s="0"/>
+      <c r="ST1" s="0"/>
+      <c r="SU1" s="0"/>
+      <c r="SV1" s="0"/>
+      <c r="SW1" s="0"/>
+      <c r="SX1" s="0"/>
+      <c r="SY1" s="0"/>
+      <c r="SZ1" s="0"/>
+      <c r="TA1" s="0"/>
+      <c r="TB1" s="0"/>
+      <c r="TC1" s="0"/>
+      <c r="TD1" s="0"/>
+      <c r="TE1" s="0"/>
+      <c r="TF1" s="0"/>
+      <c r="TG1" s="0"/>
+      <c r="TH1" s="0"/>
+      <c r="TI1" s="0"/>
+      <c r="TJ1" s="0"/>
+      <c r="TK1" s="0"/>
+      <c r="TL1" s="0"/>
+      <c r="TM1" s="0"/>
+      <c r="TN1" s="0"/>
+      <c r="TO1" s="0"/>
+      <c r="TP1" s="0"/>
+      <c r="TQ1" s="0"/>
+      <c r="TR1" s="0"/>
+      <c r="TS1" s="0"/>
+      <c r="TT1" s="0"/>
+      <c r="TU1" s="0"/>
+      <c r="TV1" s="0"/>
+      <c r="TW1" s="0"/>
+      <c r="TX1" s="0"/>
+      <c r="TY1" s="0"/>
+      <c r="TZ1" s="0"/>
+      <c r="UA1" s="0"/>
+      <c r="UB1" s="0"/>
+      <c r="UC1" s="0"/>
+      <c r="UD1" s="0"/>
+      <c r="UE1" s="0"/>
+      <c r="UF1" s="0"/>
+      <c r="UG1" s="0"/>
+      <c r="UH1" s="0"/>
+      <c r="UI1" s="0"/>
+      <c r="UJ1" s="0"/>
+      <c r="UK1" s="0"/>
+      <c r="UL1" s="0"/>
+      <c r="UM1" s="0"/>
+      <c r="UN1" s="0"/>
+      <c r="UO1" s="0"/>
+      <c r="UP1" s="0"/>
+      <c r="UQ1" s="0"/>
+      <c r="UR1" s="0"/>
+      <c r="US1" s="0"/>
+      <c r="UT1" s="0"/>
+      <c r="UU1" s="0"/>
+      <c r="UV1" s="0"/>
+      <c r="UW1" s="0"/>
+      <c r="UX1" s="0"/>
+      <c r="UY1" s="0"/>
+      <c r="UZ1" s="0"/>
+      <c r="VA1" s="0"/>
+      <c r="VB1" s="0"/>
+      <c r="VC1" s="0"/>
+      <c r="VD1" s="0"/>
+      <c r="VE1" s="0"/>
+      <c r="VF1" s="0"/>
+      <c r="VG1" s="0"/>
+      <c r="VH1" s="0"/>
+      <c r="VI1" s="0"/>
+      <c r="VJ1" s="0"/>
+      <c r="VK1" s="0"/>
+      <c r="VL1" s="0"/>
+      <c r="VM1" s="0"/>
+      <c r="VN1" s="0"/>
+      <c r="VO1" s="0"/>
+      <c r="VP1" s="0"/>
+      <c r="VQ1" s="0"/>
+      <c r="VR1" s="0"/>
+      <c r="VS1" s="0"/>
+      <c r="VT1" s="0"/>
+      <c r="VU1" s="0"/>
+      <c r="VV1" s="0"/>
+      <c r="VW1" s="0"/>
+      <c r="VX1" s="0"/>
+      <c r="VY1" s="0"/>
+      <c r="VZ1" s="0"/>
+      <c r="WA1" s="0"/>
+      <c r="WB1" s="0"/>
+      <c r="WC1" s="0"/>
+      <c r="WD1" s="0"/>
+      <c r="WE1" s="0"/>
+      <c r="WF1" s="0"/>
+      <c r="WG1" s="0"/>
+      <c r="WH1" s="0"/>
+      <c r="WI1" s="0"/>
+      <c r="WJ1" s="0"/>
+      <c r="WK1" s="0"/>
+      <c r="WL1" s="0"/>
+      <c r="WM1" s="0"/>
+      <c r="WN1" s="0"/>
+      <c r="WO1" s="0"/>
+      <c r="WP1" s="0"/>
+      <c r="WQ1" s="0"/>
+      <c r="WR1" s="0"/>
+      <c r="WS1" s="0"/>
+      <c r="WT1" s="0"/>
+      <c r="WU1" s="0"/>
+      <c r="WV1" s="0"/>
+      <c r="WW1" s="0"/>
+      <c r="WX1" s="0"/>
+      <c r="WY1" s="0"/>
+      <c r="WZ1" s="0"/>
+      <c r="XA1" s="0"/>
+      <c r="XB1" s="0"/>
+      <c r="XC1" s="0"/>
+      <c r="XD1" s="0"/>
+      <c r="XE1" s="0"/>
+      <c r="XF1" s="0"/>
+      <c r="XG1" s="0"/>
+      <c r="XH1" s="0"/>
+      <c r="XI1" s="0"/>
+      <c r="XJ1" s="0"/>
+      <c r="XK1" s="0"/>
+      <c r="XL1" s="0"/>
+      <c r="XM1" s="0"/>
+      <c r="XN1" s="0"/>
+      <c r="XO1" s="0"/>
+      <c r="XP1" s="0"/>
+      <c r="XQ1" s="0"/>
+      <c r="XR1" s="0"/>
+      <c r="XS1" s="0"/>
+      <c r="XT1" s="0"/>
+      <c r="XU1" s="0"/>
+      <c r="XV1" s="0"/>
+      <c r="XW1" s="0"/>
+      <c r="XX1" s="0"/>
+      <c r="XY1" s="0"/>
+      <c r="XZ1" s="0"/>
+      <c r="YA1" s="0"/>
+      <c r="YB1" s="0"/>
+      <c r="YC1" s="0"/>
+      <c r="YD1" s="0"/>
+      <c r="YE1" s="0"/>
+      <c r="YF1" s="0"/>
+      <c r="YG1" s="0"/>
+      <c r="YH1" s="0"/>
+      <c r="YI1" s="0"/>
+      <c r="YJ1" s="0"/>
+      <c r="YK1" s="0"/>
+      <c r="YL1" s="0"/>
+      <c r="YM1" s="0"/>
+      <c r="YN1" s="0"/>
+      <c r="YO1" s="0"/>
+      <c r="YP1" s="0"/>
+      <c r="YQ1" s="0"/>
+      <c r="YR1" s="0"/>
+      <c r="YS1" s="0"/>
+      <c r="YT1" s="0"/>
+      <c r="YU1" s="0"/>
+      <c r="YV1" s="0"/>
+      <c r="YW1" s="0"/>
+      <c r="YX1" s="0"/>
+      <c r="YY1" s="0"/>
+      <c r="YZ1" s="0"/>
+      <c r="ZA1" s="0"/>
+      <c r="ZB1" s="0"/>
+      <c r="ZC1" s="0"/>
+      <c r="ZD1" s="0"/>
+      <c r="ZE1" s="0"/>
+      <c r="ZF1" s="0"/>
+      <c r="ZG1" s="0"/>
+      <c r="ZH1" s="0"/>
+      <c r="ZI1" s="0"/>
+      <c r="ZJ1" s="0"/>
+      <c r="ZK1" s="0"/>
+      <c r="ZL1" s="0"/>
+      <c r="ZM1" s="0"/>
+      <c r="ZN1" s="0"/>
+      <c r="ZO1" s="0"/>
+      <c r="ZP1" s="0"/>
+      <c r="ZQ1" s="0"/>
+      <c r="ZR1" s="0"/>
+      <c r="ZS1" s="0"/>
+      <c r="ZT1" s="0"/>
+      <c r="ZU1" s="0"/>
+      <c r="ZV1" s="0"/>
+      <c r="ZW1" s="0"/>
+      <c r="ZX1" s="0"/>
+      <c r="ZY1" s="0"/>
+      <c r="ZZ1" s="0"/>
+      <c r="AAA1" s="0"/>
+      <c r="AAB1" s="0"/>
+      <c r="AAC1" s="0"/>
+      <c r="AAD1" s="0"/>
+      <c r="AAE1" s="0"/>
+      <c r="AAF1" s="0"/>
+      <c r="AAG1" s="0"/>
+      <c r="AAH1" s="0"/>
+      <c r="AAI1" s="0"/>
+      <c r="AAJ1" s="0"/>
+      <c r="AAK1" s="0"/>
+      <c r="AAL1" s="0"/>
+      <c r="AAM1" s="0"/>
+      <c r="AAN1" s="0"/>
+      <c r="AAO1" s="0"/>
+      <c r="AAP1" s="0"/>
+      <c r="AAQ1" s="0"/>
+      <c r="AAR1" s="0"/>
+      <c r="AAS1" s="0"/>
+      <c r="AAT1" s="0"/>
+      <c r="AAU1" s="0"/>
+      <c r="AAV1" s="0"/>
+      <c r="AAW1" s="0"/>
+      <c r="AAX1" s="0"/>
+      <c r="AAY1" s="0"/>
+      <c r="AAZ1" s="0"/>
+      <c r="ABA1" s="0"/>
+      <c r="ABB1" s="0"/>
+      <c r="ABC1" s="0"/>
+      <c r="ABD1" s="0"/>
+      <c r="ABE1" s="0"/>
+      <c r="ABF1" s="0"/>
+      <c r="ABG1" s="0"/>
+      <c r="ABH1" s="0"/>
+      <c r="ABI1" s="0"/>
+      <c r="ABJ1" s="0"/>
+      <c r="ABK1" s="0"/>
+      <c r="ABL1" s="0"/>
+      <c r="ABM1" s="0"/>
+      <c r="ABN1" s="0"/>
+      <c r="ABO1" s="0"/>
+      <c r="ABP1" s="0"/>
+      <c r="ABQ1" s="0"/>
+      <c r="ABR1" s="0"/>
+      <c r="ABS1" s="0"/>
+      <c r="ABT1" s="0"/>
+      <c r="ABU1" s="0"/>
+      <c r="ABV1" s="0"/>
+      <c r="ABW1" s="0"/>
+      <c r="ABX1" s="0"/>
+      <c r="ABY1" s="0"/>
+      <c r="ABZ1" s="0"/>
+      <c r="ACA1" s="0"/>
+      <c r="ACB1" s="0"/>
+      <c r="ACC1" s="0"/>
+      <c r="ACD1" s="0"/>
+      <c r="ACE1" s="0"/>
+      <c r="ACF1" s="0"/>
+      <c r="ACG1" s="0"/>
+      <c r="ACH1" s="0"/>
+      <c r="ACI1" s="0"/>
+      <c r="ACJ1" s="0"/>
+      <c r="ACK1" s="0"/>
+      <c r="ACL1" s="0"/>
+      <c r="ACM1" s="0"/>
+      <c r="ACN1" s="0"/>
+      <c r="ACO1" s="0"/>
+      <c r="ACP1" s="0"/>
+      <c r="ACQ1" s="0"/>
+      <c r="ACR1" s="0"/>
+      <c r="ACS1" s="0"/>
+      <c r="ACT1" s="0"/>
+      <c r="ACU1" s="0"/>
+      <c r="ACV1" s="0"/>
+      <c r="ACW1" s="0"/>
+      <c r="ACX1" s="0"/>
+      <c r="ACY1" s="0"/>
+      <c r="ACZ1" s="0"/>
+      <c r="ADA1" s="0"/>
+      <c r="ADB1" s="0"/>
+      <c r="ADC1" s="0"/>
+      <c r="ADD1" s="0"/>
+      <c r="ADE1" s="0"/>
+      <c r="ADF1" s="0"/>
+      <c r="ADG1" s="0"/>
+      <c r="ADH1" s="0"/>
+      <c r="ADI1" s="0"/>
+      <c r="ADJ1" s="0"/>
+      <c r="ADK1" s="0"/>
+      <c r="ADL1" s="0"/>
+      <c r="ADM1" s="0"/>
+      <c r="ADN1" s="0"/>
+      <c r="ADO1" s="0"/>
+      <c r="ADP1" s="0"/>
+      <c r="ADQ1" s="0"/>
+      <c r="ADR1" s="0"/>
+      <c r="ADS1" s="0"/>
+      <c r="ADT1" s="0"/>
+      <c r="ADU1" s="0"/>
+      <c r="ADV1" s="0"/>
+      <c r="ADW1" s="0"/>
+      <c r="ADX1" s="0"/>
+      <c r="ADY1" s="0"/>
+      <c r="ADZ1" s="0"/>
+      <c r="AEA1" s="0"/>
+      <c r="AEB1" s="0"/>
+      <c r="AEC1" s="0"/>
+      <c r="AED1" s="0"/>
+      <c r="AEE1" s="0"/>
+      <c r="AEF1" s="0"/>
+      <c r="AEG1" s="0"/>
+      <c r="AEH1" s="0"/>
+      <c r="AEI1" s="0"/>
+      <c r="AEJ1" s="0"/>
+      <c r="AEK1" s="0"/>
+      <c r="AEL1" s="0"/>
+      <c r="AEM1" s="0"/>
+      <c r="AEN1" s="0"/>
+      <c r="AEO1" s="0"/>
+      <c r="AEP1" s="0"/>
+      <c r="AEQ1" s="0"/>
+      <c r="AER1" s="0"/>
+      <c r="AES1" s="0"/>
+      <c r="AET1" s="0"/>
+      <c r="AEU1" s="0"/>
+      <c r="AEV1" s="0"/>
+      <c r="AEW1" s="0"/>
+      <c r="AEX1" s="0"/>
+      <c r="AEY1" s="0"/>
+      <c r="AEZ1" s="0"/>
+      <c r="AFA1" s="0"/>
+      <c r="AFB1" s="0"/>
+      <c r="AFC1" s="0"/>
+      <c r="AFD1" s="0"/>
+      <c r="AFE1" s="0"/>
+      <c r="AFF1" s="0"/>
+      <c r="AFG1" s="0"/>
+      <c r="AFH1" s="0"/>
+      <c r="AFI1" s="0"/>
+      <c r="AFJ1" s="0"/>
+      <c r="AFK1" s="0"/>
+      <c r="AFL1" s="0"/>
+      <c r="AFM1" s="0"/>
+      <c r="AFN1" s="0"/>
+      <c r="AFO1" s="0"/>
+      <c r="AFP1" s="0"/>
+      <c r="AFQ1" s="0"/>
+      <c r="AFR1" s="0"/>
+      <c r="AFS1" s="0"/>
+      <c r="AFT1" s="0"/>
+      <c r="AFU1" s="0"/>
+      <c r="AFV1" s="0"/>
+      <c r="AFW1" s="0"/>
+      <c r="AFX1" s="0"/>
+      <c r="AFY1" s="0"/>
+      <c r="AFZ1" s="0"/>
+      <c r="AGA1" s="0"/>
+      <c r="AGB1" s="0"/>
+      <c r="AGC1" s="0"/>
+      <c r="AGD1" s="0"/>
+      <c r="AGE1" s="0"/>
+      <c r="AGF1" s="0"/>
+      <c r="AGG1" s="0"/>
+      <c r="AGH1" s="0"/>
+      <c r="AGI1" s="0"/>
+      <c r="AGJ1" s="0"/>
+      <c r="AGK1" s="0"/>
+      <c r="AGL1" s="0"/>
+      <c r="AGM1" s="0"/>
+      <c r="AGN1" s="0"/>
+      <c r="AGO1" s="0"/>
+      <c r="AGP1" s="0"/>
+      <c r="AGQ1" s="0"/>
+      <c r="AGR1" s="0"/>
+      <c r="AGS1" s="0"/>
+      <c r="AGT1" s="0"/>
+      <c r="AGU1" s="0"/>
+      <c r="AGV1" s="0"/>
+      <c r="AGW1" s="0"/>
+      <c r="AGX1" s="0"/>
+      <c r="AGY1" s="0"/>
+      <c r="AGZ1" s="0"/>
+      <c r="AHA1" s="0"/>
+      <c r="AHB1" s="0"/>
+      <c r="AHC1" s="0"/>
+      <c r="AHD1" s="0"/>
+      <c r="AHE1" s="0"/>
+      <c r="AHF1" s="0"/>
+      <c r="AHG1" s="0"/>
+      <c r="AHH1" s="0"/>
+      <c r="AHI1" s="0"/>
+      <c r="AHJ1" s="0"/>
+      <c r="AHK1" s="0"/>
+      <c r="AHL1" s="0"/>
+      <c r="AHM1" s="0"/>
+      <c r="AHN1" s="0"/>
+      <c r="AHO1" s="0"/>
+      <c r="AHP1" s="0"/>
+      <c r="AHQ1" s="0"/>
+      <c r="AHR1" s="0"/>
+      <c r="AHS1" s="0"/>
+      <c r="AHT1" s="0"/>
+      <c r="AHU1" s="0"/>
+      <c r="AHV1" s="0"/>
+      <c r="AHW1" s="0"/>
+      <c r="AHX1" s="0"/>
+      <c r="AHY1" s="0"/>
+      <c r="AHZ1" s="0"/>
+      <c r="AIA1" s="0"/>
+      <c r="AIB1" s="0"/>
+      <c r="AIC1" s="0"/>
+      <c r="AID1" s="0"/>
+      <c r="AIE1" s="0"/>
+      <c r="AIF1" s="0"/>
+      <c r="AIG1" s="0"/>
+      <c r="AIH1" s="0"/>
+      <c r="AII1" s="0"/>
+      <c r="AIJ1" s="0"/>
+      <c r="AIK1" s="0"/>
+      <c r="AIL1" s="0"/>
+      <c r="AIM1" s="0"/>
+      <c r="AIN1" s="0"/>
+      <c r="AIO1" s="0"/>
+      <c r="AIP1" s="0"/>
+      <c r="AIQ1" s="0"/>
+      <c r="AIR1" s="0"/>
+      <c r="AIS1" s="0"/>
+      <c r="AIT1" s="0"/>
+      <c r="AIU1" s="0"/>
+      <c r="AIV1" s="0"/>
+      <c r="AIW1" s="0"/>
+      <c r="AIX1" s="0"/>
+      <c r="AIY1" s="0"/>
+      <c r="AIZ1" s="0"/>
+      <c r="AJA1" s="0"/>
+      <c r="AJB1" s="0"/>
+      <c r="AJC1" s="0"/>
+      <c r="AJD1" s="0"/>
+      <c r="AJE1" s="0"/>
+      <c r="AJF1" s="0"/>
+      <c r="AJG1" s="0"/>
+      <c r="AJH1" s="0"/>
+      <c r="AJI1" s="0"/>
+      <c r="AJJ1" s="0"/>
+      <c r="AJK1" s="0"/>
+      <c r="AJL1" s="0"/>
+      <c r="AJM1" s="0"/>
+      <c r="AJN1" s="0"/>
+      <c r="AJO1" s="0"/>
+      <c r="AJP1" s="0"/>
+      <c r="AJQ1" s="0"/>
+      <c r="AJR1" s="0"/>
+      <c r="AJS1" s="0"/>
+      <c r="AJT1" s="0"/>
+      <c r="AJU1" s="0"/>
+      <c r="AJV1" s="0"/>
+      <c r="AJW1" s="0"/>
+      <c r="AJX1" s="0"/>
+      <c r="AJY1" s="0"/>
+      <c r="AJZ1" s="0"/>
+      <c r="AKA1" s="0"/>
+      <c r="AKB1" s="0"/>
+      <c r="AKC1" s="0"/>
+      <c r="AKD1" s="0"/>
+      <c r="AKE1" s="0"/>
+      <c r="AKF1" s="0"/>
+      <c r="AKG1" s="0"/>
+      <c r="AKH1" s="0"/>
+      <c r="AKI1" s="0"/>
+      <c r="AKJ1" s="0"/>
+      <c r="AKK1" s="0"/>
+      <c r="AKL1" s="0"/>
+      <c r="AKM1" s="0"/>
+      <c r="AKN1" s="0"/>
+      <c r="AKO1" s="0"/>
+      <c r="AKP1" s="0"/>
+      <c r="AKQ1" s="0"/>
+      <c r="AKR1" s="0"/>
+      <c r="AKS1" s="0"/>
+      <c r="AKT1" s="0"/>
+      <c r="AKU1" s="0"/>
+      <c r="AKV1" s="0"/>
+      <c r="AKW1" s="0"/>
+      <c r="AKX1" s="0"/>
+      <c r="AKY1" s="0"/>
+      <c r="AKZ1" s="0"/>
+      <c r="ALA1" s="0"/>
+      <c r="ALB1" s="0"/>
+      <c r="ALC1" s="0"/>
+      <c r="ALD1" s="0"/>
+      <c r="ALE1" s="0"/>
+      <c r="ALF1" s="0"/>
+      <c r="ALG1" s="0"/>
+      <c r="ALH1" s="0"/>
+      <c r="ALI1" s="0"/>
+      <c r="ALJ1" s="0"/>
+      <c r="ALK1" s="0"/>
+      <c r="ALL1" s="0"/>
+      <c r="ALM1" s="0"/>
+      <c r="ALN1" s="0"/>
+      <c r="ALO1" s="0"/>
+      <c r="ALP1" s="0"/>
+      <c r="ALQ1" s="0"/>
+      <c r="ALR1" s="0"/>
+      <c r="ALS1" s="0"/>
+      <c r="ALT1" s="0"/>
+      <c r="ALU1" s="0"/>
+      <c r="ALV1" s="0"/>
+      <c r="ALW1" s="0"/>
+      <c r="ALX1" s="0"/>
+      <c r="ALY1" s="0"/>
+      <c r="ALZ1" s="0"/>
+      <c r="AMA1" s="0"/>
+      <c r="AMB1" s="0"/>
+      <c r="AMC1" s="0"/>
+      <c r="AMD1" s="0"/>
+      <c r="AME1" s="0"/>
+      <c r="AMF1" s="0"/>
+      <c r="AMG1" s="0"/>
+      <c r="AMH1" s="0"/>
+      <c r="AMI1" s="0"/>
+      <c r="AMJ1" s="0"/>
+      <c r="AMK1" s="0"/>
+      <c r="AML1" s="0"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H2" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E5" s="6" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1616,4 +2843,39 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B5:B30"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>